--- a/集训文件2/附件3_Port位置数据.xlsx
+++ b/集训文件2/附件3_Port位置数据.xlsx
@@ -1,177 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Desktop\带pygame版（让路机制完善）\OHT数学建模题_精简场景\赛题附件\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76510E5D-BE27-4F48-B8A7-9268EF624BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Port" sheetId="1" r:id="rId1"/>
+    <sheet name="Port" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>LocationID</t>
-  </si>
-  <si>
-    <t>NodeID</t>
-  </si>
-  <si>
-    <t>LinkID</t>
-  </si>
-  <si>
-    <t>Distance</t>
-  </si>
-  <si>
-    <t>P01</t>
-  </si>
-  <si>
-    <t>P02</t>
-  </si>
-  <si>
-    <t>P03</t>
-  </si>
-  <si>
-    <t>P04</t>
-  </si>
-  <si>
-    <t>P05</t>
-  </si>
-  <si>
-    <t>P06</t>
-  </si>
-  <si>
-    <t>P07</t>
-  </si>
-  <si>
-    <t>P08</t>
-  </si>
-  <si>
-    <t>P09</t>
-  </si>
-  <si>
-    <t>P10</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>P13</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>P15</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>P17</t>
-  </si>
-  <si>
-    <t>P18</t>
-  </si>
-  <si>
-    <t>P19</t>
-  </si>
-  <si>
-    <t>P20</t>
-  </si>
-  <si>
-    <t>P21</t>
-  </si>
-  <si>
-    <t>P22</t>
-  </si>
-  <si>
-    <t>P23</t>
-  </si>
-  <si>
-    <t>P24</t>
-  </si>
-  <si>
-    <t>P25</t>
-  </si>
-  <si>
-    <t>P26</t>
-  </si>
-  <si>
-    <t>P27</t>
-  </si>
-  <si>
-    <t>P28</t>
-  </si>
-  <si>
-    <t>P29</t>
-  </si>
-  <si>
-    <t>P30</t>
-  </si>
-  <si>
-    <t>P31</t>
-  </si>
-  <si>
-    <t>P32</t>
-  </si>
-  <si>
-    <t>P33</t>
-  </si>
-  <si>
-    <t>P34</t>
-  </si>
-  <si>
-    <t>P35</t>
-  </si>
-  <si>
-    <t>P36</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -195,25 +65,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,534 +477,618 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="4" width="10" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LocationID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>NodeID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LinkID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>552</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>5530</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>548</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>292</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>9</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>546</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>1092</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>10</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>650</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>12841</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>650</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5051</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>11</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>653</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1040</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>652</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>4495</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>25</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>534</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>5150</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>26</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>535</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>126.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>28</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>539</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>7857.8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>28</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>539</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>20716.7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>43</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>199</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>1772</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>50</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>522</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>5530</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>53</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>515</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>20693</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>53</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>515</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>8064.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>68</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>504</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>5150</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>69</v>
-      </c>
-      <c r="C18">
-        <v>505</v>
-      </c>
-      <c r="D18">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>70</v>
       </c>
-      <c r="C19">
+      <c r="C18" t="n">
         <v>507</v>
       </c>
-      <c r="D19">
+      <c r="D18" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>70</v>
+      </c>
+      <c r="C19" t="n">
+        <v>507</v>
+      </c>
+      <c r="D19" t="n">
         <v>583</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>71</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>509</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>7818.5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>71</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>509</v>
       </c>
-      <c r="D21">
-        <v>20686.400000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22">
+      <c r="D21" t="n">
+        <v>20686.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>45</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>200</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>7689</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>80</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>493</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>4854</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>83</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>488</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>20593</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>83</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>488</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>8230</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>94</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>478</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>4681</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>97</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>483</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>7846</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>97</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>483</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>20726</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>98</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>485</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>42.9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>113</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>461</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>4550</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>114</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>457</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>992</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>116</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>454</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>20635</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>116</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>454</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>7965</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>127</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>443</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>5205</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P34</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>129</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>446</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>896</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P35</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>130</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>448</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>7343</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37">
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P36</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>130</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>448</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>20646</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>